--- a/results/final_20260514_v2_summary/Water-quality_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/Water-quality_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.3747±0.0056</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.3367±0.0186</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2817±0.0210</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.2183±0.0322</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.7519±0.0071</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.7400±0.0063</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.7151±0.0084</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.6711±0.0089</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.6462±0.0223</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.6114±0.0211</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.5591±0.0199</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.4921±0.0189</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6277±0.0122</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.6350±0.0128</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.6363±0.0141</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6087±0.0166</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6095±0.0138</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5941±0.0147</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.5664±0.0131</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5161±0.0151</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.7336±0.0068</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.7152±0.0066</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.6813±0.0071</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6273±0.0092</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.4683±0.0129</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.4512±0.0138</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.4226±0.0125</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.3733±0.0131</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5551±0.0152</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5557±0.0153</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5394±0.0154</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5008±0.0162</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6028±0.0347</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.5719±0.0325</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5194±0.0247</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.4583±0.0204</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5471±0.0097</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5619±0.0100</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5719±0.0125</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5601±0.0172</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7751±0.0394</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6746±0.0522</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.5990±0.0433</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.4556±0.0947</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6273±0.0102</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6158±0.0112</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5896±0.0098</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5405±0.0136</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6415±0.0212</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.6104±0.0212</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5595±0.0185</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.4914±0.0190</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.6143±0.0124</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.6219±0.0104</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.6238±0.0109</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6012±0.0143</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.0387±0.0075</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.0234±0.0090</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.0151±0.0088</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0053±0.0056</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.0369±0.0063</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.0228±0.0087</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0151±0.0088</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0053±0.0056</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.3433±0.0120</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.3085±0.0146</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2624±0.0222</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.2057±0.0310</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.7489±0.0077</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.7340±0.0076</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.7068±0.0087</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.6633±0.0094</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6272±0.0266</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.5919±0.0211</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.5436±0.0194</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.4835±0.0185</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6602±0.0121</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6679±0.0153</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6663±0.0130</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6388±0.0159</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6161±0.0176</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5997±0.0163</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.5702±0.0132</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.5221±0.0149</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.7301±0.0076</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.7083±0.0087</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6717±0.0075</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6180±0.0096</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.4742±0.0168</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.4566±0.0157</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.4257±0.0124</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.3785±0.0126</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.5737±0.0169</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.5702±0.0182</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.5486±0.0151</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.5100±0.0157</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5871±0.0345</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.5562±0.0305</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.5069±0.0230</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.4519±0.0196</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.5871±0.0069</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6021±0.0137</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6071±0.0128</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.5934±0.0161</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7144±0.0488</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.6054±0.0527</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.5563±0.0428</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.4487±0.0797</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6379±0.0123</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6238±0.0136</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.5949±0.0106</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.5473±0.0133</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6253±0.0234</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.5927±0.0211</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.5441±0.0181</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.4824±0.0184</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6516±0.0065</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6590±0.0131</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6568±0.0113</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6331±0.0130</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.0311±0.0087</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.0196±0.0070</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.0126±0.0095</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0053±0.0056</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.0293±0.0082</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.0191±0.0072</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0126±0.0095</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0053±0.0056</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.3740±0.0054</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.3351±0.0193</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2796±0.0210</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.2176±0.0313</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.7519±0.0065</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.7396±0.0063</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.7144±0.0082</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.6710±0.0085</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6454±0.0226</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.6105±0.0211</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.5581±0.0200</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.4917±0.0179</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6271±0.0115</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.6343±0.0124</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.6350±0.0145</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.6079±0.0158</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6086±0.0135</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5934±0.0146</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.5653±0.0134</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.5156±0.0139</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.7335±0.0061</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.7148±0.0068</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.6805±0.0069</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6272±0.0082</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.4671±0.0126</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.4503±0.0136</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.4216±0.0127</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.3728±0.0119</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.5553±0.0139</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.5551±0.0156</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.5386±0.0154</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.5007±0.0150</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.6031±0.0338</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.5711±0.0324</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.5183±0.0246</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.4582±0.0195</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5469±0.0082</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5613±0.0105</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5712±0.0123</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5599±0.0162</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.7742±0.0372</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.6739±0.0506</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.5951±0.0459</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.4477±0.0936</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6271±0.0090</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6151±0.0113</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5886±0.0099</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.5403±0.0122</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6416±0.0207</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.6098±0.0211</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.5585±0.0186</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.4912±0.0180</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.6138±0.0115</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.6211±0.0106</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.6227±0.0106</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.6008±0.0132</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.0377±0.0079</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.0226±0.0088</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.0155±0.0094</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0051±0.0055</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.0359±0.0071</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.0221±0.0086</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0155±0.0094</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0051±0.0055</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.3432±0.0111</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.3076±0.0148</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2612±0.0231</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.2066±0.0320</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.7487±0.0085</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.7334±0.0075</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.7062±0.0086</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.6631±0.0095</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6266±0.0259</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5908±0.0209</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.5428±0.0201</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.4834±0.0179</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6606±0.0114</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.6681±0.0153</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.6665±0.0137</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.6400±0.0152</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6159±0.0169</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5991±0.0163</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.5698±0.0140</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.5225±0.0143</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.7299±0.0084</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.7077±0.0086</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.6711±0.0075</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6179±0.0094</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.4741±0.0162</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.4561±0.0157</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.4254±0.0132</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.3788±0.0122</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.5739±0.0170</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.5701±0.0181</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.5484±0.0162</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.5104±0.0155</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5869±0.0341</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.5554±0.0299</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.5062±0.0241</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.4518±0.0194</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.5876±0.0074</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.6026±0.0139</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.6075±0.0131</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.5946±0.0158</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.7149±0.0470</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.6035±0.0545</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.5556±0.0436</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.4477±0.0816</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.6380±0.0124</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.6234±0.0135</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.5946±0.0113</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.5478±0.0128</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6250±0.0230</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.5917±0.0207</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.5434±0.0189</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.4823±0.0181</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.6520±0.0068</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.6593±0.0132</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.6571±0.0108</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.6344±0.0124</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.0311±0.0087</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.0196±0.0077</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.0128±0.0098</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0053±0.0059</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.0293±0.0082</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.0191±0.0080</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0128±0.0098</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0053±0.0059</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.4601±0.0080</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.4281±0.0183</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.3757±0.0223</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.2991±0.0277</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.7361±0.0078</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.7220±0.0065</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.6958±0.0074</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.6489±0.0085</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.6738±0.0207</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.6446±0.0236</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.5911±0.0243</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.5171±0.0227</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5384±0.0110</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5392±0.0133</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5387±0.0150</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.5229±0.0180</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.5717±0.0076</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5588±0.0129</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.5360±0.0152</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.4928±0.0177</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.7326±0.0078</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.7187±0.0066</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.6936±0.0074</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.6479±0.0085</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.4271±0.0067</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4153±0.0111</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.3914±0.0142</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.3493±0.0148</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.4980±0.0118</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.4973±0.0139</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.4929±0.0164</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.4681±0.0184</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.6350±0.0342</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.5982±0.0359</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.5422±0.0300</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.4757±0.0250</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.4499±0.0076</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4558±0.0115</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4675±0.0133</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.4690±0.0179</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.8825±0.0157</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.8245±0.0436</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.7348±0.0518</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.6039±0.0780</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.5857±0.0086</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.5733±0.0108</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.5528±0.0126</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.5122±0.0159</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.6735±0.0195</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.6420±0.0217</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.5897±0.0228</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.5150±0.0232</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.5185±0.0105</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.5183±0.0125</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.5206±0.0117</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.5098±0.0144</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.0264±0.0048</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.0200±0.0062</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.0113±0.0075</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0017±0.0029</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.0264±0.0048</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.0200±0.0062</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0113±0.0075</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0017±0.0029</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.3075±0.0182</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.2762±0.0194</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.2463±0.0230</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.2510±0.0287</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.7223±0.0048</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.6953±0.0060</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.6529±0.0101</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.5900±0.0090</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6032±0.0204</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.5616±0.0208</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.5098±0.0204</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.4533±0.0139</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6724±0.0131</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.6976±0.0125</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7203±0.0128</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.7288±0.0167</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6094±0.0102</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.5967±0.0136</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.5725±0.0148</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.5351±0.0129</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.7179±0.0050</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.6912±0.0062</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.6497±0.0098</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.5881±0.0090</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.4655±0.0095</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.4506±0.0132</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.4244±0.0139</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.3866±0.0108</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.5833±0.0112</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.5761±0.0144</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.5602±0.0171</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.5317±0.0129</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5710±0.0270</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.5299±0.0241</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.4835±0.0223</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.4355±0.0152</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.6152±0.0095</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.6434±0.0127</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.6729±0.0136</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.6941±0.0163</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.6059±0.0509</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.5509±0.0635</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.5788±0.0812</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.5806±0.0742</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6345±0.0077</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.6212±0.0101</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.5985±0.0126</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.5617±0.0116</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6024±0.0178</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.5625±0.0181</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.5139±0.0191</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.4577±0.0144</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.6708±0.0122</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.6943±0.0120</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7172±0.0112</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7274±0.0152</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.0160±0.0048</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.0121±0.0068</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.0036±0.0038</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0006±0.0015</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.0160±0.0048</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.0121±0.0068</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0036±0.0038</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0006±0.0015</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.5093±0.0122</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.4681±0.0173</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.4049±0.0217</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.3201±0.0262</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.7307±0.0081</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.7199±0.0070</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.6947±0.0076</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.6482±0.0090</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.6899±0.0225</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.6564±0.0248</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.5996±0.0268</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.5196±0.0215</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.4947±0.0084</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5042±0.0119</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5077±0.0143</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4960±0.0161</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.5474±0.0075</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5415±0.0128</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.5214±0.0165</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.4799±0.0162</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.7269±0.0081</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.7164±0.0071</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.6925±0.0074</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.6471±0.0090</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.4034±0.0076</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.3985±0.0113</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.3773±0.0151</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.3380±0.0138</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.4617±0.0140</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.4723±0.0147</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.4751±0.0183</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.4544±0.0185</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.6368±0.0478</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.6034±0.0379</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.5447±0.0329</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.4751±0.0254</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4006±0.0052</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.4186±0.0110</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.4364±0.0142</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.4430±0.0172</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.9066±0.0332</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.8570±0.0432</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.7603±0.0499</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.6275±0.0800</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.5559±0.0090</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.5528±0.0112</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.5358±0.0143</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.4976±0.0153</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.6834±0.0247</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.6512±0.0240</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.5947±0.0257</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.5148±0.0225</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.4689±0.0067</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.4806±0.0108</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.4879±0.0113</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.4820±0.0135</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.0236±0.0052</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.0213±0.0076</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.0117±0.0081</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0019±0.0038</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.0236±0.0052</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.0213±0.0076</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.0117±0.0081</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0019±0.0038</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.3081±0.0201</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.2768±0.0192</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.2465±0.0229</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.2485±0.0293</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.7232±0.0052</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.6954±0.0067</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.6528±0.0099</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.5901±0.0096</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6042±0.0202</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.5620±0.0220</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.5094±0.0204</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.4532±0.0143</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6723±0.0118</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.6963±0.0130</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7184±0.0126</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.7272±0.0168</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6102±0.0100</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.5963±0.0148</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.5716±0.0146</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.5346±0.0134</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.7188±0.0053</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.6912±0.0070</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.6493±0.0097</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.5881±0.0095</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.4667±0.0093</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4502±0.0144</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.4235±0.0139</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.3861±0.0113</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.5839±0.0111</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.5756±0.0155</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.5591±0.0170</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.5316±0.0135</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5734±0.0283</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.5300±0.0249</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.4830±0.0223</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.4356±0.0156</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.6152±0.0095</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.6421±0.0128</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.6709±0.0140</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.6934±0.0161</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.6159±0.0646</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.5511±0.0663</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.5728±0.0789</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.5773±0.0721</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.6351±0.0077</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.6209±0.0112</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.5976±0.0126</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.5613±0.0120</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6037±0.0181</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.5627±0.0189</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.5137±0.0191</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.4576±0.0149</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.6706±0.0122</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.6932±0.0115</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7153±0.0119</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7262±0.0148</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.0160±0.0048</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.0121±0.0069</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.0040±0.0044</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0006±0.0015</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.0160±0.0048</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.0121±0.0069</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0040±0.0044</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0006±0.0015</t>
         </is>
